--- a/2_Formulas_Functions/8_Text_Functions.xlsx
+++ b/2_Formulas_Functions/8_Text_Functions.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarve\Desktop\Обучение\Excel_Data_Analytics_Course-main\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289F5FEB-D4A0-4E30-9E0C-8AA9F558B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79E5B56-AA9C-44D9-B0FA-4D3037FB0294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11993" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
-    <sheet name="Text_Combination" sheetId="9" r:id="rId2"/>
-    <sheet name="Text_Extraction" sheetId="10" r:id="rId3"/>
-    <sheet name="Text_Search" sheetId="11" r:id="rId4"/>
-    <sheet name="Skills" sheetId="12" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId2"/>
+    <sheet name="Text_Combination" sheetId="9" r:id="rId3"/>
+    <sheet name="Text_Extraction" sheetId="10" r:id="rId4"/>
+    <sheet name="Text_Search" sheetId="11" r:id="rId5"/>
+    <sheet name="Skills" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -598,7 +602,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Skill Count of Applicants</a:t>
+              <a:t>Chart Skill Count of Appplicants</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -636,7 +640,7 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="bar"/>
+        <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -767,7 +771,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F30C-45CA-B8A0-F5AF8B1DA29B}"/>
+              <c16:uniqueId val="{00000000-E911-455A-9FC4-0603A6DFC2A8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -779,17 +783,18 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1389519888"/>
-        <c:axId val="1389514128"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1847816560"/>
+        <c:axId val="1847817040"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1389519888"/>
+        <c:axId val="1847816560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -827,7 +832,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1389514128"/>
+        <c:crossAx val="1847817040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -835,12 +840,12 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1389514128"/>
+        <c:axId val="1847817040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -886,7 +891,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1389519888"/>
+        <c:crossAx val="1847816560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -976,7 +981,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1180,23 +1185,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1301,8 +1305,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1434,20 +1438,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1484,23 +1487,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>588963</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>35983</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>30163</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>117475</xdr:rowOff>
+      <xdr:colOff>370417</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>112183</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C6A45A-EB32-62D3-58CF-3F02DAF72B23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B55E9BB5-848F-BCF4-E2C1-02B351A5E6EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1785,27 +1788,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B5E7F13-C613-4452-9CDB-2C26D6876D9D}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="14.265625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.265625" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" customWidth="1"/>
-    <col min="10" max="10" width="34.73046875" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="15.46484375" customWidth="1"/>
-    <col min="14" max="14" width="8.86328125" customWidth="1"/>
-    <col min="15" max="15" width="16.3984375" customWidth="1"/>
-    <col min="17" max="19" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="35.42578125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" customWidth="1"/>
+    <col min="17" max="18" width="0" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1853,7 +1858,7 @@
       <c r="U1" s="17"/>
       <c r="V1" s="17"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -1877,6 +1882,21 @@
       </c>
       <c r="H2" s="6" t="s">
         <v>11</v>
+      </c>
+      <c r="J2" t="str">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,F2:G2)</f>
+        <v>457 Oak St San Jose, CA, 95101</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:M2">+_xlfn.TEXTSPLIT(B2," ",,)</f>
+        <v>Pam</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Beesly</v>
+      </c>
+      <c r="O2" t="str">
+        <f>RIGHT(A2,7)</f>
+        <v>0123548</v>
       </c>
       <c r="Q2">
         <f>FIND(",", G2)+LEN(", ")</f>
@@ -1890,8 +1910,20 @@
         <f>MID(G2,Q2,R2-Q2)</f>
         <v>CA</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T2">
+        <f>FIND(",",G2)+LEN(", ")</f>
+        <v>11</v>
+      </c>
+      <c r="U2">
+        <f>FIND(",",G2,T2)</f>
+        <v>13</v>
+      </c>
+      <c r="V2" t="str">
+        <f>MID(G2,T2,U2-T2)</f>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -1916,20 +1948,47 @@
       <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J21" si="0">_xlfn.TEXTJOIN(" ",TRUE,F3:G3)</f>
+        <v>203 Birch St Chicago, IL, 60601</v>
+      </c>
+      <c r="L3" t="str" cm="1">
+        <f t="array" ref="L3:M3">+_xlfn.TEXTSPLIT(B3," ",,)</f>
+        <v>Michael</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O21" si="1">RIGHT(A3,7)</f>
+        <v>0123549</v>
+      </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="0">FIND(",", G3)+LEN(", ")</f>
+        <f t="shared" ref="Q3:Q21" si="2">FIND(",", G3)+LEN(", ")</f>
         <v>10</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R21" si="1">FIND(",",G3,Q3)</f>
+        <f t="shared" ref="R3:R21" si="3">FIND(",",G3,Q3)</f>
         <v>12</v>
       </c>
       <c r="S3" t="str">
-        <f t="shared" ref="S3:S21" si="2">MID(G3,Q3,R3-Q3)</f>
+        <f t="shared" ref="S3:S21" si="4">MID(G3,Q3,R3-Q3)</f>
         <v>IL</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T3">
+        <f t="shared" ref="T3:T21" si="5">FIND(",",G3)+LEN(", ")</f>
+        <v>10</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U21" si="6">FIND(",",G3,T3)</f>
+        <v>12</v>
+      </c>
+      <c r="V3" t="str">
+        <f t="shared" ref="V3:V21" si="7">MID(G3,T3,U3-T3)</f>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -1954,20 +2013,47 @@
       <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>790 Pine St Chicago, IL, 60601</v>
+      </c>
+      <c r="L4" t="str" cm="1">
+        <f t="array" ref="L4:M4">+_xlfn.TEXTSPLIT(B4," ",,)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="1"/>
+        <v>0123550</v>
+      </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T4">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V4" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -1992,20 +2078,47 @@
       <c r="H5" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>457 Oak St San Jose, CA, 95101</v>
+      </c>
+      <c r="L5" t="str" cm="1">
+        <f t="array" ref="L5:M5">+_xlfn.TEXTSPLIT(B5," ",,)</f>
+        <v>Pam</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Beesly</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="1"/>
+        <v>0123551</v>
+      </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T5">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V5" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -2030,20 +2143,47 @@
       <c r="H6" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L6" t="str" cm="1">
+        <f t="array" ref="L6:M6">+_xlfn.TEXTSPLIT(B6," ",,)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="1"/>
+        <v>0123552</v>
+      </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T6">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V6" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -2068,20 +2208,47 @@
       <c r="H7" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>204 Birch St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L7" t="str" cm="1">
+        <f t="array" ref="L7:M7">+_xlfn.TEXTSPLIT(B7," ",,)</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="1"/>
+        <v>0123553</v>
+      </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T7">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V7" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -2106,20 +2273,47 @@
       <c r="H8" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>790 Pine St Chicago, IL, 60601</v>
+      </c>
+      <c r="L8" t="str" cm="1">
+        <f t="array" ref="L8:M8">+_xlfn.TEXTSPLIT(B8," ",,)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="1"/>
+        <v>0123554</v>
+      </c>
       <c r="Q8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V8" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2144,20 +2338,47 @@
       <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>204 Birch St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L9" t="str" cm="1">
+        <f t="array" ref="L9:M9">+_xlfn.TEXTSPLIT(B9," ",,)</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="1"/>
+        <v>0123555</v>
+      </c>
       <c r="Q9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T9">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V9" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2182,20 +2403,47 @@
       <c r="H10" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St Chicago, IL, 60601</v>
+      </c>
+      <c r="L10" t="str" cm="1">
+        <f t="array" ref="L10:M10">+_xlfn.TEXTSPLIT(B10," ",,)</f>
+        <v>Stanley</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Hudson</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="1"/>
+        <v>0123556</v>
+      </c>
       <c r="Q10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T10">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V10" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -2220,20 +2468,47 @@
       <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St Los Angeles, CA, 90001</v>
+      </c>
+      <c r="L11" t="str" cm="1">
+        <f t="array" ref="L11:M11">+_xlfn.TEXTSPLIT(B11," ",,)</f>
+        <v>Angela</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Martin</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="1"/>
+        <v>0123557</v>
+      </c>
       <c r="Q11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="V11" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -2258,20 +2533,47 @@
       <c r="H12" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St San Diego, CA, 92101</v>
+      </c>
+      <c r="L12" t="str" cm="1">
+        <f t="array" ref="L12:M12">+_xlfn.TEXTSPLIT(B12," ",,)</f>
+        <v>Dwight</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Schrute</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="1"/>
+        <v>0123558</v>
+      </c>
       <c r="Q12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="R12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T12">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="V12" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -2296,20 +2598,47 @@
       <c r="H13" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>202 Birch St Chicago, IL, 60601</v>
+      </c>
+      <c r="L13" t="str" cm="1">
+        <f t="array" ref="L13:M13">+_xlfn.TEXTSPLIT(B13," ",,)</f>
+        <v>Oscar</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Martinez</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="1"/>
+        <v>0123559</v>
+      </c>
       <c r="Q13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T13">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V13" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -2334,20 +2663,47 @@
       <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>204 Birch St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L14" t="str" cm="1">
+        <f t="array" ref="L14:M14">+_xlfn.TEXTSPLIT(B14," ",,)</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="1"/>
+        <v>0123560</v>
+      </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T14">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V14" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -2372,20 +2728,47 @@
       <c r="H15" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>123 Elm St Chicago, IL, 60601</v>
+      </c>
+      <c r="L15" t="str" cm="1">
+        <f t="array" ref="L15:M15">+_xlfn.TEXTSPLIT(B15," ",,)</f>
+        <v>Phyllis</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Vance</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="1"/>
+        <v>0123561</v>
+      </c>
       <c r="Q15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="T15">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V15" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -2410,20 +2793,47 @@
       <c r="H16" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>456 Oak St Chicago, IL, 60601</v>
+      </c>
+      <c r="L16" t="str" cm="1">
+        <f t="array" ref="L16:M16">+_xlfn.TEXTSPLIT(B16," ",,)</f>
+        <v>Meredith</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Palmer</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="1"/>
+        <v>0123562</v>
+      </c>
       <c r="Q16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T16">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V16" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2448,20 +2858,47 @@
       <c r="H17" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>203 Birch St Chicago, IL, 60602</v>
+      </c>
+      <c r="L17" t="str" cm="1">
+        <f t="array" ref="L17:M17">+_xlfn.TEXTSPLIT(B17," ",,)</f>
+        <v>Michael</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="1"/>
+        <v>0123563</v>
+      </c>
       <c r="Q17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T17">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V17" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -2486,20 +2923,47 @@
       <c r="H18" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L18" t="str" cm="1">
+        <f t="array" ref="L18:M18">+_xlfn.TEXTSPLIT(B18," ",,)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="1"/>
+        <v>0123564</v>
+      </c>
       <c r="Q18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T18">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V18" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -2524,20 +2988,47 @@
       <c r="H19" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>456 Oak St New York, NY, 10001</v>
+      </c>
+      <c r="L19" t="str" cm="1">
+        <f t="array" ref="L19:M19">+_xlfn.TEXTSPLIT(B19," ",,)</f>
+        <v>Kelly</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Kapoor</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="1"/>
+        <v>0123565</v>
+      </c>
       <c r="Q19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>NY</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="T19">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V19" t="str">
+        <f t="shared" si="7"/>
+        <v>NY</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -2562,20 +3053,47 @@
       <c r="H20" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St Philadelphia, PA, 19101</v>
+      </c>
+      <c r="L20" t="str" cm="1">
+        <f t="array" ref="L20:M20">+_xlfn.TEXTSPLIT(B20," ",,)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="1"/>
+        <v>0123566</v>
+      </c>
       <c r="Q20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="T20">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V20" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -2600,16 +3118,43 @@
       <c r="H21" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>459 Oak St New York, NY, 10001</v>
+      </c>
+      <c r="L21" t="str" cm="1">
+        <f t="array" ref="L21:M21">+_xlfn.TEXTSPLIT(B21," ",,)</f>
+        <v>Jim</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="1"/>
+        <v>0123567</v>
+      </c>
       <c r="Q21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
+        <v>NY</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V21" t="str">
+        <f t="shared" si="7"/>
         <v>NY</v>
       </c>
     </row>
@@ -2627,23 +3172,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC3E42D-FCEE-4796-8E08-6363E9302590}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BCB134-41DE-47D5-9456-1C60C9867AFA}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="29.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -2672,7 +3226,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -2702,7 +3256,7 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -2732,7 +3286,7 @@
         <v>203 Birch St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -2762,7 +3316,7 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -2792,7 +3346,7 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -2822,7 +3376,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -2852,7 +3406,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -2882,7 +3436,7 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2912,7 +3466,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2942,7 +3496,7 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -2972,7 +3526,7 @@
         <v>123 Elm St Los Angeles, CA, 90001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -3002,7 +3556,7 @@
         <v>123 Elm St San Diego, CA, 92101</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -3032,7 +3586,7 @@
         <v>202 Birch St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -3062,7 +3616,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -3092,7 +3646,7 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -3122,7 +3676,7 @@
         <v>456 Oak St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -3152,7 +3706,7 @@
         <v>203 Birch St Chicago, IL, 60602</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -3182,7 +3736,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -3212,7 +3766,7 @@
         <v>456 Oak St New York, NY, 10001</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -3242,7 +3796,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -3270,908 +3824,6 @@
       <c r="J21" t="str">
         <f t="shared" si="0"/>
         <v>459 Oak St New York, NY, 10001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F197DD-EE87-4022-A4E6-1027B6E64DD6}">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.59765625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11">
-        <v>44971.640451388892</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="str" cm="1">
-        <f t="array" ref="I2:J2">_xlfn.TEXTSPLIT(B2," ")</f>
-        <v>Pam</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Beesly</v>
-      </c>
-      <c r="L2" t="str" cm="1">
-        <f t="array" ref="L2:L6">_xlfn.UNIQUE(C2:C21)</f>
-        <v>Data Analyst</v>
-      </c>
-      <c r="M2" t="b">
-        <f>IF(LEN(A2)=10,TRUE,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="N2" t="str">
-        <f>RIGHT(A2,7)</f>
-        <v>0123548</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="11">
-        <v>45055.40662037037</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="str" cm="1">
-        <f t="array" ref="I3:J3">_xlfn.TEXTSPLIT(B3," ")</f>
-        <v>Michael</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Scott</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Business Intelligence Analyst</v>
-      </c>
-      <c r="M3" t="b">
-        <f t="shared" ref="M3:M21" si="0">IF(LEN(A3)=10,TRUE,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="N3" t="str">
-        <f t="shared" ref="N3:N21" si="1">RIGHT(A3,7)</f>
-        <v>0123549</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="11">
-        <v>45128.729710648149</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="str" cm="1">
-        <f t="array" ref="I4:J4">_xlfn.TEXTSPLIT(B4," ")</f>
-        <v>Kevin</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Malone</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Data Engineer</v>
-      </c>
-      <c r="M4" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N4" t="str">
-        <f t="shared" si="1"/>
-        <v>0123550</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="11">
-        <v>45173.302187499998</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="str" cm="1">
-        <f t="array" ref="I5:J5">_xlfn.TEXTSPLIT(B5," ")</f>
-        <v>Pam</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Beesly</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Data Scientist</v>
-      </c>
-      <c r="M5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N5" t="str">
-        <f t="shared" si="1"/>
-        <v>0123551</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="11">
-        <v>45248.70857638889</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" t="str" cm="1">
-        <f t="array" ref="I6:J6">_xlfn.TEXTSPLIT(B6," ")</f>
-        <v>Jim</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Halpert</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Machine Learning Engineer</v>
-      </c>
-      <c r="M6" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N6" t="str">
-        <f t="shared" si="1"/>
-        <v>0123552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="11">
-        <v>45302.531921296293</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="str" cm="1">
-        <f t="array" ref="I7:J7">_xlfn.TEXTSPLIT(B7," ")</f>
-        <v>Ryan</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Howard</v>
-      </c>
-      <c r="M7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N7" t="str">
-        <f t="shared" si="1"/>
-        <v>0123553</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="11">
-        <v>45354.687881944446</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" t="str" cm="1">
-        <f t="array" ref="I8:J8">_xlfn.TEXTSPLIT(B8," ")</f>
-        <v>Kevin</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Malone</v>
-      </c>
-      <c r="M8" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N8" t="str">
-        <f t="shared" si="1"/>
-        <v>0123554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11">
-        <v>45408.340810185182</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="str" cm="1">
-        <f t="array" ref="I9:J9">_xlfn.TEXTSPLIT(B9," ")</f>
-        <v>Ryan</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Howard</v>
-      </c>
-      <c r="M9" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N9" t="str">
-        <f t="shared" si="1"/>
-        <v>0123555</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="11">
-        <v>45458.743333333332</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="str" cm="1">
-        <f t="array" ref="I10:J10">_xlfn.TEXTSPLIT(B10," ")</f>
-        <v>Stanley</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Hudson</v>
-      </c>
-      <c r="M10" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N10" t="str">
-        <f t="shared" si="1"/>
-        <v>0123556</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="11">
-        <v>45480.608055555553</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="str" cm="1">
-        <f t="array" ref="I11:J11">_xlfn.TEXTSPLIT(B11," ")</f>
-        <v>Angela</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Martin</v>
-      </c>
-      <c r="M11" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N11" t="str">
-        <f t="shared" si="1"/>
-        <v>0123557</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="11">
-        <v>45455.284930555557</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" t="str" cm="1">
-        <f t="array" ref="I12:J12">_xlfn.TEXTSPLIT(B12," ")</f>
-        <v>Dwight</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Schrute</v>
-      </c>
-      <c r="M12" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N12" t="str">
-        <f t="shared" si="1"/>
-        <v>0123558</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="11">
-        <v>44951.552141203705</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" t="str" cm="1">
-        <f t="array" ref="I13:J13">_xlfn.TEXTSPLIT(B13," ")</f>
-        <v>Oscar</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Martinez</v>
-      </c>
-      <c r="M13" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N13" t="str">
-        <f t="shared" si="1"/>
-        <v>0123559</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A14" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>45002.490034722221</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="str" cm="1">
-        <f t="array" ref="I14:J14">_xlfn.TEXTSPLIT(B14," ")</f>
-        <v>Ryan</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Howard</v>
-      </c>
-      <c r="M14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N14" t="str">
-        <f t="shared" si="1"/>
-        <v>0123560</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="11">
-        <v>45078.417256944442</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" t="str" cm="1">
-        <f t="array" ref="I15:J15">_xlfn.TEXTSPLIT(B15," ")</f>
-        <v>Phyllis</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Vance</v>
-      </c>
-      <c r="M15" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N15" t="str">
-        <f t="shared" si="1"/>
-        <v>0123561</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="11">
-        <v>45168.729328703703</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" t="str" cm="1">
-        <f t="array" ref="I16:J16">_xlfn.TEXTSPLIT(B16," ")</f>
-        <v>Meredith</v>
-      </c>
-      <c r="J16" t="str">
-        <v>Palmer</v>
-      </c>
-      <c r="M16" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N16" t="str">
-        <f t="shared" si="1"/>
-        <v>0123562</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="11">
-        <v>45218.319780092592</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" t="str" cm="1">
-        <f t="array" ref="I17:J17">_xlfn.TEXTSPLIT(B17," ")</f>
-        <v>Michael</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Scott</v>
-      </c>
-      <c r="M17" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N17" t="str">
-        <f t="shared" si="1"/>
-        <v>0123563</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="11">
-        <v>45350.719236111108</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" t="str" cm="1">
-        <f t="array" ref="I18:J18">_xlfn.TEXTSPLIT(B18," ")</f>
-        <v>Jim</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Halpert</v>
-      </c>
-      <c r="M18" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N18" t="str">
-        <f t="shared" si="1"/>
-        <v>0123564</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A19" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="11">
-        <v>45418.726354166669</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" t="str" cm="1">
-        <f t="array" ref="I19:J19">_xlfn.TEXTSPLIT(B19," ")</f>
-        <v>Kelly</v>
-      </c>
-      <c r="J19" t="str">
-        <v>Kapoor</v>
-      </c>
-      <c r="M19" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N19" t="str">
-        <f t="shared" si="1"/>
-        <v>0123565</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A20" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="11">
-        <v>45496.291701388887</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" t="str" cm="1">
-        <f t="array" ref="I20:J20">_xlfn.TEXTSPLIT(B20," ")</f>
-        <v>Jim</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Halpert</v>
-      </c>
-      <c r="M20" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N20" t="str">
-        <f t="shared" si="1"/>
-        <v>0123566</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="12">
-        <v>45422.739884259259</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" t="str" cm="1">
-        <f t="array" ref="I21:J21">_xlfn.TEXTSPLIT(B21," ")</f>
-        <v>Jim</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Halpert</v>
-      </c>
-      <c r="M21" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N21" t="str">
-        <f t="shared" si="1"/>
-        <v>0123567</v>
       </c>
     </row>
   </sheetData>
@@ -4180,23 +3832,925 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F197DD-EE87-4022-A4E6-1027B6E64DD6}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="13"/>
+      <c r="L1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11">
+        <v>44971.640451388892</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="str" cm="1">
+        <f t="array" ref="I2:J2">_xlfn.TEXTSPLIT(B2," ")</f>
+        <v>Pam</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Beesly</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L6">_xlfn.UNIQUE(C2:C21)</f>
+        <v>Data Analyst</v>
+      </c>
+      <c r="M2" t="b">
+        <f>IF(LEN(A2)=10,TRUE,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="N2" t="str">
+        <f>RIGHT(A2,7)</f>
+        <v>0123548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11">
+        <v>45055.40662037037</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="str" cm="1">
+        <f t="array" ref="I3:J3">_xlfn.TEXTSPLIT(B3," ")</f>
+        <v>Michael</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Business Intelligence Analyst</v>
+      </c>
+      <c r="M3" t="b">
+        <f t="shared" ref="M3:M21" si="0">IF(LEN(A3)=10,TRUE,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N21" si="1">RIGHT(A3,7)</f>
+        <v>0123549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11">
+        <v>45128.729710648149</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="str" cm="1">
+        <f t="array" ref="I4:J4">_xlfn.TEXTSPLIT(B4," ")</f>
+        <v>Kevin</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Data Engineer</v>
+      </c>
+      <c r="M4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="1"/>
+        <v>0123550</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="11">
+        <v>45173.302187499998</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="str" cm="1">
+        <f t="array" ref="I5:J5">_xlfn.TEXTSPLIT(B5," ")</f>
+        <v>Pam</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Beesly</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Data Scientist</v>
+      </c>
+      <c r="M5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="1"/>
+        <v>0123551</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="11">
+        <v>45248.70857638889</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="str" cm="1">
+        <f t="array" ref="I6:J6">_xlfn.TEXTSPLIT(B6," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Machine Learning Engineer</v>
+      </c>
+      <c r="M6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="1"/>
+        <v>0123552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="11">
+        <v>45302.531921296293</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="str" cm="1">
+        <f t="array" ref="I7:J7">_xlfn.TEXTSPLIT(B7," ")</f>
+        <v>Ryan</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="M7" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="1"/>
+        <v>0123553</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="11">
+        <v>45354.687881944446</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" t="str" cm="1">
+        <f t="array" ref="I8:J8">_xlfn.TEXTSPLIT(B8," ")</f>
+        <v>Kevin</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Malone</v>
+      </c>
+      <c r="M8" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="1"/>
+        <v>0123554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11">
+        <v>45408.340810185182</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="str" cm="1">
+        <f t="array" ref="I9:J9">_xlfn.TEXTSPLIT(B9," ")</f>
+        <v>Ryan</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="M9" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="1"/>
+        <v>0123555</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="11">
+        <v>45458.743333333332</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="str" cm="1">
+        <f t="array" ref="I10:J10">_xlfn.TEXTSPLIT(B10," ")</f>
+        <v>Stanley</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Hudson</v>
+      </c>
+      <c r="M10" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="1"/>
+        <v>0123556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="11">
+        <v>45480.608055555553</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="str" cm="1">
+        <f t="array" ref="I11:J11">_xlfn.TEXTSPLIT(B11," ")</f>
+        <v>Angela</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Martin</v>
+      </c>
+      <c r="M11" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="1"/>
+        <v>0123557</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="11">
+        <v>45455.284930555557</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="str" cm="1">
+        <f t="array" ref="I12:J12">_xlfn.TEXTSPLIT(B12," ")</f>
+        <v>Dwight</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Schrute</v>
+      </c>
+      <c r="M12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="1"/>
+        <v>0123558</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="11">
+        <v>44951.552141203705</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="str" cm="1">
+        <f t="array" ref="I13:J13">_xlfn.TEXTSPLIT(B13," ")</f>
+        <v>Oscar</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Martinez</v>
+      </c>
+      <c r="M13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="1"/>
+        <v>0123559</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11">
+        <v>45002.490034722221</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="str" cm="1">
+        <f t="array" ref="I14:J14">_xlfn.TEXTSPLIT(B14," ")</f>
+        <v>Ryan</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Howard</v>
+      </c>
+      <c r="M14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="1"/>
+        <v>0123560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="11">
+        <v>45078.417256944442</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="str" cm="1">
+        <f t="array" ref="I15:J15">_xlfn.TEXTSPLIT(B15," ")</f>
+        <v>Phyllis</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Vance</v>
+      </c>
+      <c r="M15" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="1"/>
+        <v>0123561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="11">
+        <v>45168.729328703703</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="str" cm="1">
+        <f t="array" ref="I16:J16">_xlfn.TEXTSPLIT(B16," ")</f>
+        <v>Meredith</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Palmer</v>
+      </c>
+      <c r="M16" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="1"/>
+        <v>0123562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="11">
+        <v>45218.319780092592</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" t="str" cm="1">
+        <f t="array" ref="I17:J17">_xlfn.TEXTSPLIT(B17," ")</f>
+        <v>Michael</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Scott</v>
+      </c>
+      <c r="M17" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="1"/>
+        <v>0123563</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="11">
+        <v>45350.719236111108</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="str" cm="1">
+        <f t="array" ref="I18:J18">_xlfn.TEXTSPLIT(B18," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="M18" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="1"/>
+        <v>0123564</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="11">
+        <v>45418.726354166669</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" t="str" cm="1">
+        <f t="array" ref="I19:J19">_xlfn.TEXTSPLIT(B19," ")</f>
+        <v>Kelly</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Kapoor</v>
+      </c>
+      <c r="M19" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="1"/>
+        <v>0123565</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="11">
+        <v>45496.291701388887</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" t="str" cm="1">
+        <f t="array" ref="I20:J20">_xlfn.TEXTSPLIT(B20," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="M20" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="1"/>
+        <v>0123566</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="12">
+        <v>45422.739884259259</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" t="str" cm="1">
+        <f t="array" ref="I21:J21">_xlfn.TEXTSPLIT(B21," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Halpert</v>
+      </c>
+      <c r="M21" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="1"/>
+        <v>0123567</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E73CB36-69AF-4B27-BCC8-FDB353A4DE72}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" customWidth="1"/>
-    <col min="5" max="5" width="26.1328125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -4227,7 +4781,7 @@
       <c r="K1" s="17"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -4265,7 +4819,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -4303,7 +4857,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -4341,7 +4895,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -4379,7 +4933,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -4417,7 +4971,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -4455,7 +5009,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -4493,7 +5047,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -4531,7 +5085,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -4569,7 +5123,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -4607,7 +5161,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -4645,7 +5199,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -4683,7 +5237,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -4721,7 +5275,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -4759,7 +5313,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -4797,7 +5351,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -4835,7 +5389,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -4873,7 +5427,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -4911,7 +5465,7 @@
         <v>NY</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -4949,7 +5503,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -4995,33 +5549,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85789AE4-586B-4DA1-B069-1172780CDADC}">
   <dimension ref="A2:BW25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.3984375" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="16"/>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>_xlfn.TEXTJOIN(", ",TRUE,Data!H2:H21)</f>
         <v>Kafka, DataBricks, Spark, Python, GCP, Power BI, GCP, Airflow, Hadoop, R, Azure, Java, SQL, DataBricks, Kafka, DataBricks, Spark, Python, GCP, DataBricks, Hadoop, Java, Snowflake, Airflow, DataBricks, Azure, Java, SQL, DataBricks, Snowflake, Airflow, DataBricks, Scala, Azure, R, Kafka, Snowflake, Excel, Scala, Excel, Power BI, R, Scala, R, Hadoop, Power BI, SQL, Snowflake, Airflow, DataBricks, Java, Scala, R, DataBricks, Azure, Scala, Power BI, GCP, Airflow, Hadoop, R, DataBricks, Hadoop, Java, Snowflake, Power BI, Tableau, Airflow, SQL, DataBricks, Hadoop, Java, DataBricks, Hadoop, Java</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B5" s="16"/>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6" t="str" cm="1">
         <f t="array" ref="A6:BW6">_xlfn.TEXTSPLIT(A3,", ")</f>
         <v>Kafka</v>
@@ -5249,7 +5803,7 @@
         <v>Java</v>
       </c>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>68</v>
       </c>
@@ -5261,7 +5815,7 @@
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str" cm="1">
         <f t="array" ref="A9:A25">_xlfn.UNIQUE(TRANSPOSE(6:6))</f>
         <v>Kafka</v>
@@ -5271,7 +5825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <v>DataBricks</v>
       </c>
@@ -5280,7 +5834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <v>Spark</v>
       </c>
@@ -5289,7 +5843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <v>Python</v>
       </c>
@@ -5298,7 +5852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <v>GCP</v>
       </c>
@@ -5307,7 +5861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <v>Power BI</v>
       </c>
@@ -5316,7 +5870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <v>Airflow</v>
       </c>
@@ -5325,7 +5879,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <v>Hadoop</v>
       </c>
@@ -5334,7 +5888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <v>R</v>
       </c>
@@ -5343,7 +5897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <v>Azure</v>
       </c>
@@ -5352,7 +5906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <v>Java</v>
       </c>
@@ -5361,7 +5915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <v>SQL</v>
       </c>
@@ -5370,7 +5924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <v>Snowflake</v>
       </c>
@@ -5379,7 +5933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <v>Scala</v>
       </c>
@@ -5388,7 +5942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <v>Excel</v>
       </c>
@@ -5397,7 +5951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <v>Tableau</v>
       </c>
@@ -5406,7 +5960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>0</v>
       </c>
